--- a/output/CS/expanded_mapping_cosine_SkillNER RAKE_KeyBERT_CS.xlsx
+++ b/output/CS/expanded_mapping_cosine_SkillNER RAKE_KeyBERT_CS.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Graphic design 3</t>
+          <t>Graphic design 4</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Graphic design 5</t>
+          <t>Graphic design 1</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -483,7 +483,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Graphic design 1</t>
+          <t>Graphic design 5</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -498,7 +498,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Graphic design 4</t>
+          <t>Graphic design 2</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -513,7 +513,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Graphic design 2</t>
+          <t>Graphic design 3</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Problem management 4</t>
+          <t>Problem management 2</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Problem management 5</t>
+          <t>Problem management 3</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -558,7 +558,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Problem management 3</t>
+          <t>Problem management 4</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -573,7 +573,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Problem management 2</t>
+          <t>Problem management 5</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -588,7 +588,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Measurement 3</t>
+          <t>Measurement 2</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Measurement 2</t>
+          <t>Measurement 3</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Measurement 3</t>
+          <t>Measurement 6</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Measurement 2</t>
+          <t>Measurement 5</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Measurement 5</t>
+          <t>Measurement 2</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Measurement 6</t>
+          <t>Measurement 3</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Infrastructure operations 3</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -738,7 +738,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 4</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Infrastructure operations 4</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -768,7 +768,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 3</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -783,7 +783,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Data engineering 3</t>
+          <t>Data engineering 2</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -828,7 +828,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Data engineering 2</t>
+          <t>Data engineering 3</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>User acceptance testing 2</t>
+          <t>User acceptance testing 6</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>User acceptance testing 3</t>
+          <t>User acceptance testing 5</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>User acceptance testing 6</t>
+          <t>User acceptance testing 3</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>User acceptance testing 5</t>
+          <t>User acceptance testing 2</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Incident management 1</t>
+          <t>Incident management 4</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Incident management 4</t>
+          <t>Incident management 2</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Incident management 2</t>
+          <t>Incident management 3</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Incident management 3</t>
+          <t>Incident management 1</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>User acceptance testing 5</t>
+          <t>User acceptance testing 3</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>User acceptance testing 4</t>
+          <t>User acceptance testing 5</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>User acceptance testing 2</t>
+          <t>User acceptance testing 4</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>User acceptance testing 3</t>
+          <t>User acceptance testing 2</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Incident management 2</t>
+          <t>Incident management 3</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Incident management 3</t>
+          <t>Incident management 5</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Incident management 5</t>
+          <t>Incident management 2</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Solution architecture 4</t>
+          <t>Solution architecture 6</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Solution architecture 6</t>
+          <t>Solution architecture 4</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Enterprise and business architecture 5</t>
+          <t>Enterprise and business architecture 6</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Enterprise and business architecture 6</t>
+          <t>Enterprise and business architecture 5</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Machine learning 3</t>
+          <t>Machine learning 2</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Machine learning 2</t>
+          <t>Machine learning 5</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Machine learning 5</t>
+          <t>Machine learning 3</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Machine learning 2</t>
+          <t>Machine learning 6</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Machine learning 4</t>
+          <t>Machine learning 2</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Machine learning 6</t>
+          <t>Machine learning 4</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Machine learning 3</t>
+          <t>Machine learning 2</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Machine learning 2</t>
+          <t>Machine learning 5</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Machine learning 5</t>
+          <t>Machine learning 3</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Machine learning 2</t>
+          <t>Machine learning 6</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Machine learning 4</t>
+          <t>Machine learning 2</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Machine learning 6</t>
+          <t>Machine learning 4</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Database administration 3</t>
+          <t>Database administration 2</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Database administration 2</t>
+          <t>Database administration 3</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Database design 2</t>
+          <t>Database design 3</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Database design 5</t>
+          <t>Database design 4</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Database design 4</t>
+          <t>Database design 2</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Database design 3</t>
+          <t>Database design 5</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Data engineering 3</t>
+          <t>Data engineering 4</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Data engineering 4</t>
+          <t>Data engineering 2</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Data engineering 2</t>
+          <t>Data engineering 3</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sales support 6</t>
+          <t>Sales support 4</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sales support 4</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sales support 5</t>
+          <t>Sales support 6</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 5</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Customer service support 2</t>
+          <t>Customer service support 1</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Customer service support 1</t>
+          <t>Customer service support 2</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Information management 4</t>
+          <t>Information management 5</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Information management 3</t>
+          <t>Information management 6</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Information management 5</t>
+          <t>Information management 4</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Information management 6</t>
+          <t>Information management 3</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Business situation analysis 2</t>
+          <t>Business situation analysis 3</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Business situation analysis 3</t>
+          <t>Business situation analysis 2</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Business administration 4</t>
+          <t>Business administration 5</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Business administration 3</t>
+          <t>Business administration 4</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Business administration 1</t>
+          <t>Business administration 3</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Business administration 5</t>
+          <t>Business administration 1</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Business situation analysis 5</t>
+          <t>Business situation analysis 4</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Business situation analysis 2</t>
+          <t>Business situation analysis 6</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Business situation analysis 4</t>
+          <t>Business situation analysis 5</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Business situation analysis 6</t>
+          <t>Business situation analysis 2</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>User acceptance testing 2</t>
+          <t>User acceptance testing 3</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>User acceptance testing 3</t>
+          <t>User acceptance testing 2</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Business process improvement 4</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 4</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Business process improvement 5</t>
+          <t>Business process improvement 4</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 5</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Business process improvement 4</t>
+          <t>Business process improvement 7</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Business process improvement 7</t>
+          <t>Business process improvement 6</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Business process improvement 6</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Business process improvement 5</t>
+          <t>Business process improvement 4</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 5</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Business process improvement 4</t>
+          <t>Business process improvement 6</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Business process improvement 6</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Business process improvement 4</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Business process improvement 5</t>
+          <t>Business process improvement 4</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 5</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Network design 4</t>
+          <t>Network design 6</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Network design 6</t>
+          <t>Network design 4</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 5</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Network design 5</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>High-performance computing 5</t>
+          <t>High-performance computing 6</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>High-performance computing 6</t>
+          <t>High-performance computing 5</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>High-performance computing 7</t>
+          <t>High-performance computing 6</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>High-performance computing 5</t>
+          <t>High-performance computing 4</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>High-performance computing 4</t>
+          <t>High-performance computing 5</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>High-performance computing 6</t>
+          <t>High-performance computing 7</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>High-performance computing 5</t>
+          <t>High-performance computing 4</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>High-performance computing 4</t>
+          <t>High-performance computing 5</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Real-time/embedded systems development 6</t>
+          <t>Real-time/embedded systems development 4</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Real-time/embedded systems development 4</t>
+          <t>Real-time/embedded systems development 2</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Real-time/embedded systems development 2</t>
+          <t>Real-time/embedded systems development 6</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Application support 3</t>
+          <t>Application support 5</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Application support 2</t>
+          <t>Application support 3</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Application support 5</t>
+          <t>Application support 4</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Application support 4</t>
+          <t>Application support 2</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Storage management 2</t>
+          <t>Storage management 3</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Storage management 3</t>
+          <t>Storage management 2</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 5</t>
+          <t>Systems and software lifecycle engineering 3</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 3</t>
+          <t>Systems and software lifecycle engineering 5</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Data engineering 3</t>
+          <t>Data engineering 2</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Data engineering 2</t>
+          <t>Data engineering 3</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Sales support 6</t>
+          <t>Sales support 4</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Sales support 4</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Sales support 5</t>
+          <t>Sales support 6</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 5</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Sales support 3</t>
+          <t>Sales support 4</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Sales support 4</t>
+          <t>Sales support 3</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Sales support 5</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 5</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Strategic planning 4</t>
+          <t>Strategic planning 7</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Strategic planning 7</t>
+          <t>Strategic planning 6</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Strategic planning 6</t>
+          <t>Strategic planning 4</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 3</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Sales support 1</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Sales support 3</t>
+          <t>Sales support 1</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Strategic planning 4</t>
+          <t>Strategic planning 5</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Strategic planning 5</t>
+          <t>Strategic planning 4</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Data science 5</t>
+          <t>Data science 4</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Data science 4</t>
+          <t>Data science 5</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Data analytics 5</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Data analytics 4</t>
+          <t>Data analytics 6</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Data analytics 6</t>
+          <t>Data analytics 5</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 4</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Marketing campaign management 4</t>
+          <t>Marketing campaign management 3</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Marketing campaign management 3</t>
+          <t>Marketing campaign management 4</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Security operations 3</t>
+          <t>Security operations 6</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Security operations 4</t>
+          <t>Security operations 2</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Security operations 6</t>
+          <t>Security operations 4</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Security operations 5</t>
+          <t>Security operations 1</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Security operations 1</t>
+          <t>Security operations 3</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Security operations 2</t>
+          <t>Security operations 5</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 3</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Sales support 1</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Sales support 3</t>
+          <t>Sales support 1</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Financial analysis 6</t>
+          <t>Financial analysis 3</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Financial analysis 2</t>
+          <t>Financial analysis 6</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Financial analysis 3</t>
+          <t>Financial analysis 4</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Financial analysis 4</t>
+          <t>Financial analysis 2</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Data management 3</t>
+          <t>Data management 2</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Data management 2</t>
+          <t>Data management 4</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Data management 4</t>
+          <t>Data management 3</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Knowledge management 2</t>
+          <t>Knowledge management 3</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Knowledge management 3</t>
+          <t>Knowledge management 2</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Infrastructure operations 3</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 3</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Data modelling and design 2</t>
+          <t>Data modelling and design 4</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Data modelling and design 4</t>
+          <t>Data modelling and design 2</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Database design 2</t>
+          <t>Database design 3</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Database design 5</t>
+          <t>Database design 4</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Database design 4</t>
+          <t>Database design 2</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Database design 3</t>
+          <t>Database design 5</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Data engineering 3</t>
+          <t>Data engineering 2</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Data engineering 2</t>
+          <t>Data engineering 3</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Data engineering 3</t>
+          <t>Data engineering 4</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Data engineering 4</t>
+          <t>Data engineering 2</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Data engineering 2</t>
+          <t>Data engineering 3</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Database design 2</t>
+          <t>Database design 3</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Database design 3</t>
+          <t>Database design 2</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Data visualisation 5</t>
+          <t>Data visualisation 4</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Data visualisation 4</t>
+          <t>Data visualisation 5</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Data engineering 3</t>
+          <t>Data engineering 2</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Data engineering 2</t>
+          <t>Data engineering 3</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Data analytics 5</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Data analytics 4</t>
+          <t>Data analytics 6</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Data analytics 6</t>
+          <t>Data analytics 5</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 4</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Database design 2</t>
+          <t>Database design 3</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Database design 5</t>
+          <t>Database design 4</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Database design 4</t>
+          <t>Database design 2</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Database design 3</t>
+          <t>Database design 5</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Graphic design 2</t>
+          <t>Graphic design 3</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Graphic design 3</t>
+          <t>Graphic design 2</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Graphic design 3</t>
+          <t>Graphic design 4</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Graphic design 5</t>
+          <t>Graphic design 1</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Graphic design 1</t>
+          <t>Graphic design 5</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Graphic design 4</t>
+          <t>Graphic design 2</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Graphic design 2</t>
+          <t>Graphic design 3</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Emerging technology monitoring 5</t>
+          <t>Emerging technology monitoring 6</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Emerging technology monitoring 6</t>
+          <t>Emerging technology monitoring 4</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Emerging technology monitoring 4</t>
+          <t>Emerging technology monitoring 5</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Security operations 3</t>
+          <t>Security operations 2</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Security operations 5</t>
+          <t>Security operations 1</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Security operations 1</t>
+          <t>Security operations 3</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Security operations 2</t>
+          <t>Security operations 5</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Configuration management 2</t>
+          <t>Configuration management 5</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Configuration management 3</t>
+          <t>Configuration management 4</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Configuration management 4</t>
+          <t>Configuration management 3</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Configuration management 5</t>
+          <t>Configuration management 2</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Configuration management 2</t>
+          <t>Configuration management 4</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Configuration management 4</t>
+          <t>Configuration management 2</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Database administration 3</t>
+          <t>Database administration 2</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Database administration 2</t>
+          <t>Database administration 3</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Measurement 3</t>
+          <t>Measurement 6</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Measurement 2</t>
+          <t>Measurement 5</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Measurement 5</t>
+          <t>Measurement 2</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Measurement 6</t>
+          <t>Measurement 3</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Configuration management 5</t>
+          <t>Configuration management 4</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Configuration management 4</t>
+          <t>Configuration management 5</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Machine learning 3</t>
+          <t>Machine learning 2</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Machine learning 2</t>
+          <t>Machine learning 5</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Machine learning 5</t>
+          <t>Machine learning 3</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Machine learning 2</t>
+          <t>Machine learning 6</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Machine learning 4</t>
+          <t>Machine learning 2</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Machine learning 6</t>
+          <t>Machine learning 4</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Deployment 3</t>
+          <t>Deployment 2</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Deployment 2</t>
+          <t>Deployment 6</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Deployment 6</t>
+          <t>Deployment 3</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Business situation analysis 5</t>
+          <t>Business situation analysis 3</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Business situation analysis 2</t>
+          <t>Business situation analysis 5</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Business situation analysis 3</t>
+          <t>Business situation analysis 2</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Functional testing 3</t>
+          <t>Functional testing 2</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Functional testing 2</t>
+          <t>Functional testing 3</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Functional testing 3</t>
+          <t>Functional testing 2</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Functional testing 2</t>
+          <t>Functional testing 4</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Functional testing 4</t>
+          <t>Functional testing 3</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>User acceptance testing 2</t>
+          <t>User acceptance testing 3</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>User acceptance testing 3</t>
+          <t>User acceptance testing 2</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Database administration 3</t>
+          <t>Database administration 2</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Database administration 2</t>
+          <t>Database administration 3</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Database design 2</t>
+          <t>Database design 3</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Database design 5</t>
+          <t>Database design 4</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Database design 4</t>
+          <t>Database design 2</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Database design 3</t>
+          <t>Database design 5</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Database design 2</t>
+          <t>Database design 3</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Database design 3</t>
+          <t>Database design 2</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>User experience design 6</t>
+          <t>User experience design 5</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>User experience design 5</t>
+          <t>User experience design 6</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Graphic design 3</t>
+          <t>Graphic design 4</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Graphic design 5</t>
+          <t>Graphic design 1</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Graphic design 1</t>
+          <t>Graphic design 5</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Graphic design 4</t>
+          <t>Graphic design 2</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Graphic design 2</t>
+          <t>Graphic design 3</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Data analytics 5</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Data analytics 4</t>
+          <t>Data analytics 6</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Data analytics 6</t>
+          <t>Data analytics 5</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 4</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Data engineering 3</t>
+          <t>Data engineering 4</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Data engineering 4</t>
+          <t>Data engineering 2</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Data engineering 2</t>
+          <t>Data engineering 3</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Data analytics 5</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 4</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Data analytics 4</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 5</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Data analytics 5</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Data analytics 4</t>
+          <t>Data analytics 7</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 5</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Data analytics 7</t>
+          <t>Data analytics 4</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Machine learning 3</t>
+          <t>Machine learning 2</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Machine learning 2</t>
+          <t>Machine learning 3</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Application support 3</t>
+          <t>Application support 5</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Application support 2</t>
+          <t>Application support 3</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Application support 5</t>
+          <t>Application support 4</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Application support 4</t>
+          <t>Application support 2</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Application support 3</t>
+          <t>Application support 5</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Application support 2</t>
+          <t>Application support 3</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Application support 5</t>
+          <t>Application support 4</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Application support 4</t>
+          <t>Application support 2</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 5</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Penetration testing 5</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Information management 4</t>
+          <t>Information management 5</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Information management 3</t>
+          <t>Information management 6</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Information management 5</t>
+          <t>Information management 4</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Information management 6</t>
+          <t>Information management 3</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 5</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Penetration testing 5</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Deployment 3</t>
+          <t>Deployment 2</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Deployment 2</t>
+          <t>Deployment 6</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Deployment 6</t>
+          <t>Deployment 3</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Business process improvement 4</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 4</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Business process improvement 4</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Business process improvement 5</t>
+          <t>Business process improvement 4</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 5</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Business process improvement 5</t>
+          <t>Business process improvement 4</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 5</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Business process improvement 4</t>
+          <t>Business process improvement 7</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Business process improvement 7</t>
+          <t>Business process improvement 6</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Business process improvement 6</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Business situation analysis 2</t>
+          <t>Business situation analysis 3</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Business situation analysis 3</t>
+          <t>Business situation analysis 2</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Information management 4</t>
+          <t>Information management 5</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Information management 3</t>
+          <t>Information management 6</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Information management 5</t>
+          <t>Information management 4</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Information management 6</t>
+          <t>Information management 3</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Audit 2</t>
+          <t>Audit 3</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Audit 6</t>
+          <t>Audit 4</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Audit 4</t>
+          <t>Audit 5</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Audit 5</t>
+          <t>Audit 2</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Audit 3</t>
+          <t>Audit 6</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Information management 6</t>
+          <t>Information management 5</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Information management 5</t>
+          <t>Information management 6</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Audit 2</t>
+          <t>Audit 3</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Audit 6</t>
+          <t>Audit 4</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Audit 4</t>
+          <t>Audit 5</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Audit 5</t>
+          <t>Audit 2</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Audit 3</t>
+          <t>Audit 6</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Audit 2</t>
+          <t>Audit 3</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Audit 6</t>
+          <t>Audit 4</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Audit 4</t>
+          <t>Audit 5</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Audit 5</t>
+          <t>Audit 2</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Audit 3</t>
+          <t>Audit 6</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 7</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 6</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Risk management 6</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Risk management 7</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 7</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 6</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Risk management 6</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Risk management 7</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 7</t>
         </is>
       </c>
       <c r="C580" t="n">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 6</t>
         </is>
       </c>
       <c r="C581" t="n">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Risk management 6</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C582" t="n">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Risk management 7</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C584" t="n">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C590" t="n">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C591" t="n">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C592" t="n">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C593" t="n">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C594" t="n">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 6</t>
         </is>
       </c>
       <c r="C596" t="n">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C597" t="n">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Risk management 6</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C598" t="n">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C599" t="n">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Knowledge management 2</t>
+          <t>Knowledge management 3</t>
         </is>
       </c>
       <c r="C603" t="n">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Knowledge management 3</t>
+          <t>Knowledge management 2</t>
         </is>
       </c>
       <c r="C605" t="n">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C606" t="n">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C607" t="n">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C608" t="n">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C609" t="n">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 7</t>
         </is>
       </c>
       <c r="C614" t="n">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 6</t>
         </is>
       </c>
       <c r="C615" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Risk management 6</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Risk management 7</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C618" t="n">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C622" t="n">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C623" t="n">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Audit 2</t>
+          <t>Audit 3</t>
         </is>
       </c>
       <c r="C631" t="n">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Audit 6</t>
+          <t>Audit 4</t>
         </is>
       </c>
       <c r="C632" t="n">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Audit 4</t>
+          <t>Audit 5</t>
         </is>
       </c>
       <c r="C633" t="n">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Audit 5</t>
+          <t>Audit 2</t>
         </is>
       </c>
       <c r="C634" t="n">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Audit 3</t>
+          <t>Audit 6</t>
         </is>
       </c>
       <c r="C635" t="n">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 6</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C638" t="n">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Risk management 6</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C639" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C640" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Organisational facilitation 5</t>
+          <t>Organisational facilitation 6</t>
         </is>
       </c>
       <c r="C642" t="n">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Organisational facilitation 4</t>
+          <t>Organisational facilitation 5</t>
         </is>
       </c>
       <c r="C643" t="n">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Organisational facilitation 6</t>
+          <t>Organisational facilitation 4</t>
         </is>
       </c>
       <c r="C644" t="n">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Information security 5</t>
+          <t>Information security 3</t>
         </is>
       </c>
       <c r="C645" t="n">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Information security 2</t>
+          <t>Information security 6</t>
         </is>
       </c>
       <c r="C646" t="n">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Information security 6</t>
+          <t>Information security 5</t>
         </is>
       </c>
       <c r="C647" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Information security 3</t>
+          <t>Information security 4</t>
         </is>
       </c>
       <c r="C648" t="n">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Information security 4</t>
+          <t>Information security 2</t>
         </is>
       </c>
       <c r="C649" t="n">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Software design 5</t>
+          <t>Software design 6</t>
         </is>
       </c>
       <c r="C651" t="n">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Software design 3</t>
+          <t>Software design 5</t>
         </is>
       </c>
       <c r="C652" t="n">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Software design 6</t>
+          <t>Software design 3</t>
         </is>
       </c>
       <c r="C654" t="n">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Information management 4</t>
+          <t>Information management 5</t>
         </is>
       </c>
       <c r="C655" t="n">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Information management 3</t>
+          <t>Information management 6</t>
         </is>
       </c>
       <c r="C656" t="n">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Information management 5</t>
+          <t>Information management 4</t>
         </is>
       </c>
       <c r="C657" t="n">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Information management 6</t>
+          <t>Information management 3</t>
         </is>
       </c>
       <c r="C658" t="n">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C661" t="n">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C662" t="n">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C663" t="n">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C669" t="n">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C670" t="n">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C671" t="n">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C672" t="n">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Hardware design 4</t>
+          <t>Hardware design 5</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Hardware design 5</t>
+          <t>Hardware design 4</t>
         </is>
       </c>
       <c r="C677" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C678" t="n">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C679" t="n">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C681" t="n">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C682" t="n">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Quality assurance 6</t>
+          <t>Quality assurance 5</t>
         </is>
       </c>
       <c r="C683" t="n">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Quality assurance 5</t>
+          <t>Quality assurance 3</t>
         </is>
       </c>
       <c r="C685" t="n">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Quality assurance 3</t>
+          <t>Quality assurance 4</t>
         </is>
       </c>
       <c r="C686" t="n">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Quality assurance 4</t>
+          <t>Quality assurance 6</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Information assurance 3</t>
+          <t>Information assurance 2</t>
         </is>
       </c>
       <c r="C690" t="n">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Information assurance 2</t>
+          <t>Information assurance 3</t>
         </is>
       </c>
       <c r="C691" t="n">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Information security 5</t>
+          <t>Information security 2</t>
         </is>
       </c>
       <c r="C693" t="n">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Information security 2</t>
+          <t>Information security 5</t>
         </is>
       </c>
       <c r="C694" t="n">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Information security 5</t>
+          <t>Information security 3</t>
         </is>
       </c>
       <c r="C696" t="n">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Information security 2</t>
+          <t>Information security 6</t>
         </is>
       </c>
       <c r="C697" t="n">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Information security 7</t>
+          <t>Information security 5</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Information security 6</t>
+          <t>Information security 7</t>
         </is>
       </c>
       <c r="C699" t="n">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Information security 3</t>
+          <t>Information security 4</t>
         </is>
       </c>
       <c r="C700" t="n">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Information security 4</t>
+          <t>Information security 2</t>
         </is>
       </c>
       <c r="C701" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C702" t="n">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C703" t="n">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Customer service support 2</t>
+          <t>Customer service support 1</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Customer service support 1</t>
+          <t>Customer service support 2</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C706" t="n">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Marketing management 4</t>
+          <t>Marketing management 5</t>
         </is>
       </c>
       <c r="C710" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Marketing management 5</t>
+          <t>Marketing management 4</t>
         </is>
       </c>
       <c r="C711" t="n">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Marketing management 6</t>
+          <t>Marketing management 5</t>
         </is>
       </c>
       <c r="C712" t="n">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Marketing management 5</t>
+          <t>Marketing management 6</t>
         </is>
       </c>
       <c r="C714" t="n">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Storage management 2</t>
+          <t>Storage management 3</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Storage management 4</t>
+          <t>Storage management 2</t>
         </is>
       </c>
       <c r="C718" t="n">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Storage management 3</t>
+          <t>Storage management 4</t>
         </is>
       </c>
       <c r="C719" t="n">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Service level management 3</t>
+          <t>Service level management 2</t>
         </is>
       </c>
       <c r="C720" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Service level management 2</t>
+          <t>Service level management 3</t>
         </is>
       </c>
       <c r="C721" t="n">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Product management 3</t>
+          <t>Product management 4</t>
         </is>
       </c>
       <c r="C729" t="n">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Product management 4</t>
+          <t>Product management 3</t>
         </is>
       </c>
       <c r="C731" t="n">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Product management 3</t>
+          <t>Product management 4</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Product management 4</t>
+          <t>Product management 3</t>
         </is>
       </c>
       <c r="C734" t="n">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Product management 2</t>
+          <t>Product management 3</t>
         </is>
       </c>
       <c r="C736" t="n">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Product management 3</t>
+          <t>Product management 6</t>
         </is>
       </c>
       <c r="C737" t="n">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Product management 6</t>
+          <t>Product management 2</t>
         </is>
       </c>
       <c r="C740" t="n">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Programming/software development 2</t>
+          <t>Programming/software development 6</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Programming/software development 6</t>
+          <t>Programming/software development 3</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Programming/software development 3</t>
+          <t>Programming/software development 2</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Information management 6</t>
+          <t>Information management 5</t>
         </is>
       </c>
       <c r="C749" t="n">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Information management 5</t>
+          <t>Information management 6</t>
         </is>
       </c>
       <c r="C751" t="n">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Information management 4</t>
+          <t>Information management 5</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Information management 3</t>
+          <t>Information management 6</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Information management 5</t>
+          <t>Information management 4</t>
         </is>
       </c>
       <c r="C756" t="n">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Information management 6</t>
+          <t>Information management 3</t>
         </is>
       </c>
       <c r="C757" t="n">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Process testing 2</t>
+          <t>Process testing 1</t>
         </is>
       </c>
       <c r="C761" t="n">
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Process testing 4</t>
+          <t>Process testing 3</t>
         </is>
       </c>
       <c r="C762" t="n">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Process testing 3</t>
+          <t>Process testing 2</t>
         </is>
       </c>
       <c r="C763" t="n">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Process testing 1</t>
+          <t>Process testing 4</t>
         </is>
       </c>
       <c r="C764" t="n">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>System software administration 2</t>
+          <t>System software administration 4</t>
         </is>
       </c>
       <c r="C765" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>System software administration 4</t>
+          <t>System software administration 2</t>
         </is>
       </c>
       <c r="C767" t="n">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C768" t="n">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C769" t="n">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C772" t="n">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C773" t="n">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C774" t="n">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C775" t="n">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C776" t="n">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Availability management 6</t>
+          <t>Availability management 4</t>
         </is>
       </c>
       <c r="C777" t="n">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Availability management 4</t>
+          <t>Availability management 6</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C781" t="n">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C782" t="n">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C786" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C788" t="n">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 5</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>Penetration testing 5</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C792" t="n">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C794" t="n">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 5</t>
         </is>
       </c>
       <c r="C797" t="n">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Penetration testing 5</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C798" t="n">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C799" t="n">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Information security 5</t>
+          <t>Information security 2</t>
         </is>
       </c>
       <c r="C804" t="n">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Information security 2</t>
+          <t>Information security 5</t>
         </is>
       </c>
       <c r="C805" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Systems installation and removal 1</t>
+          <t>Systems installation and removal 3</t>
         </is>
       </c>
       <c r="C810" t="n">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Systems installation and removal 2</t>
+          <t>Systems installation and removal 1</t>
         </is>
       </c>
       <c r="C811" t="n">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Systems installation and removal 3</t>
+          <t>Systems installation and removal 4</t>
         </is>
       </c>
       <c r="C812" t="n">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Systems installation and removal 4</t>
+          <t>Systems installation and removal 2</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Business intelligence 4</t>
+          <t>Business intelligence 3</t>
         </is>
       </c>
       <c r="C818" t="n">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Business intelligence 5</t>
+          <t>Business intelligence 4</t>
         </is>
       </c>
       <c r="C819" t="n">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Business intelligence 3</t>
+          <t>Business intelligence 5</t>
         </is>
       </c>
       <c r="C821" t="n">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Sales support 6</t>
+          <t>Sales support 4</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Sales support 4</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C826" t="n">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Sales support 5</t>
+          <t>Sales support 6</t>
         </is>
       </c>
       <c r="C827" t="n">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 5</t>
         </is>
       </c>
       <c r="C828" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 5</t>
+          <t>Systems and software lifecycle engineering 3</t>
         </is>
       </c>
       <c r="C831" t="n">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 3</t>
+          <t>Systems and software lifecycle engineering 5</t>
         </is>
       </c>
       <c r="C832" t="n">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>User experience evaluation 4</t>
+          <t>User experience evaluation 2</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>User experience evaluation 3</t>
+          <t>User experience evaluation 4</t>
         </is>
       </c>
       <c r="C835" t="n">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>User experience evaluation 2</t>
+          <t>User experience evaluation 3</t>
         </is>
       </c>
       <c r="C837" t="n">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 5</t>
+          <t>Systems and software lifecycle engineering 3</t>
         </is>
       </c>
       <c r="C838" t="n">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 6</t>
+          <t>Systems and software lifecycle engineering 5</t>
         </is>
       </c>
       <c r="C839" t="n">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 3</t>
+          <t>Systems and software lifecycle engineering 4</t>
         </is>
       </c>
       <c r="C840" t="n">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 4</t>
+          <t>Systems and software lifecycle engineering 6</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Hardware design 2</t>
+          <t>Hardware design 3</t>
         </is>
       </c>
       <c r="C849" t="n">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Hardware design 3</t>
+          <t>Hardware design 4</t>
         </is>
       </c>
       <c r="C850" t="n">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>Hardware design 4</t>
+          <t>Hardware design 2</t>
         </is>
       </c>
       <c r="C852" t="n">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Hardware design 4</t>
+          <t>Hardware design 5</t>
         </is>
       </c>
       <c r="C854" t="n">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Hardware design 5</t>
+          <t>Hardware design 4</t>
         </is>
       </c>
       <c r="C857" t="n">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Hardware design 2</t>
+          <t>Hardware design 3</t>
         </is>
       </c>
       <c r="C858" t="n">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Hardware design 3</t>
+          <t>Hardware design 4</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Hardware design 4</t>
+          <t>Hardware design 2</t>
         </is>
       </c>
       <c r="C860" t="n">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Hardware design 2</t>
+          <t>Hardware design 3</t>
         </is>
       </c>
       <c r="C861" t="n">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Hardware design 3</t>
+          <t>Hardware design 2</t>
         </is>
       </c>
       <c r="C862" t="n">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>Information security 5</t>
+          <t>Information security 2</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>Information security 2</t>
+          <t>Information security 5</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Financial management 4</t>
+          <t>Financial management 5</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Financial management 5</t>
+          <t>Financial management 4</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Information and data compliance 5</t>
+          <t>Information and data compliance 4</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>Information and data compliance 4</t>
+          <t>Information and data compliance 5</t>
         </is>
       </c>
       <c r="C874" t="n">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Change control 2</t>
+          <t>Change control 3</t>
         </is>
       </c>
       <c r="C875" t="n">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Change control 5</t>
+          <t>Change control 6</t>
         </is>
       </c>
       <c r="C876" t="n">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Change control 6</t>
+          <t>Change control 4</t>
         </is>
       </c>
       <c r="C877" t="n">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>Change control 4</t>
+          <t>Change control 2</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Change control 3</t>
+          <t>Change control 5</t>
         </is>
       </c>
       <c r="C879" t="n">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>Programming/software development 4</t>
+          <t>Programming/software development 2</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Programming/software development 2</t>
+          <t>Programming/software development 4</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Software design 5</t>
+          <t>Software design 6</t>
         </is>
       </c>
       <c r="C885" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>Software design 3</t>
+          <t>Software design 5</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>Software design 6</t>
+          <t>Software design 3</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Software design 2</t>
+          <t>Software design 3</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>Software design 4</t>
+          <t>Software design 2</t>
         </is>
       </c>
       <c r="C890" t="n">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Software design 3</t>
+          <t>Software design 4</t>
         </is>
       </c>
       <c r="C891" t="n">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>User experience design 6</t>
+          <t>User experience design 5</t>
         </is>
       </c>
       <c r="C892" t="n">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>User experience design 5</t>
+          <t>User experience design 6</t>
         </is>
       </c>
       <c r="C895" t="n">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Identity and access management 3</t>
+          <t>Identity and access management 4</t>
         </is>
       </c>
       <c r="C899" t="n">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>Identity and access management 2</t>
+          <t>Identity and access management 3</t>
         </is>
       </c>
       <c r="C900" t="n">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Identity and access management 1</t>
+          <t>Identity and access management 2</t>
         </is>
       </c>
       <c r="C901" t="n">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>Identity and access management 4</t>
+          <t>Identity and access management 1</t>
         </is>
       </c>
       <c r="C902" t="n">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>User experience evaluation 4</t>
+          <t>User experience evaluation 2</t>
         </is>
       </c>
       <c r="C903" t="n">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>User experience evaluation 3</t>
+          <t>User experience evaluation 4</t>
         </is>
       </c>
       <c r="C904" t="n">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>User experience evaluation 2</t>
+          <t>User experience evaluation 3</t>
         </is>
       </c>
       <c r="C906" t="n">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>Storage management 2</t>
+          <t>Storage management 3</t>
         </is>
       </c>
       <c r="C907" t="n">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>Storage management 3</t>
+          <t>Storage management 2</t>
         </is>
       </c>
       <c r="C908" t="n">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C910" t="n">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C911" t="n">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C912" t="n">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C913" t="n">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Systems design 2</t>
+          <t>Systems design 3</t>
         </is>
       </c>
       <c r="C919" t="n">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>Systems design 3</t>
+          <t>Systems design 2</t>
         </is>
       </c>
       <c r="C920" t="n">
@@ -14238,7 +14238,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>User experience design 6</t>
+          <t>User experience design 5</t>
         </is>
       </c>
       <c r="C921" t="n">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>User experience design 5</t>
+          <t>User experience design 6</t>
         </is>
       </c>
       <c r="C924" t="n">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C927" t="n">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C928" t="n">
@@ -14358,7 +14358,7 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C929" t="n">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C930" t="n">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C931" t="n">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C932" t="n">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C933" t="n">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C934" t="n">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 5</t>
         </is>
       </c>
       <c r="C935" t="n">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>Network design 5</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C936" t="n">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C938" t="n">
@@ -14508,7 +14508,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 5</t>
         </is>
       </c>
       <c r="C939" t="n">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>Network design 5</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C940" t="n">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C942" t="n">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 5</t>
         </is>
       </c>
       <c r="C943" t="n">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>Network design 5</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C944" t="n">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C946" t="n">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C947" t="n">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C949" t="n">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C950" t="n">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C951" t="n">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C952" t="n">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C954" t="n">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C955" t="n">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C956" t="n">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C957" t="n">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 5</t>
         </is>
       </c>
       <c r="C959" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>Network design 5</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C960" t="n">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C962" t="n">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C963" t="n">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C964" t="n">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C965" t="n">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C966" t="n">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C967" t="n">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C968" t="n">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C970" t="n">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C971" t="n">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C972" t="n">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C973" t="n">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Network design 4</t>
+          <t>Network design 6</t>
         </is>
       </c>
       <c r="C977" t="n">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>Network design 6</t>
+          <t>Network design 4</t>
         </is>
       </c>
       <c r="C978" t="n">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C979" t="n">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C980" t="n">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C981" t="n">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C982" t="n">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C984" t="n">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C986" t="n">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>Customer service support 2</t>
+          <t>Customer service support 1</t>
         </is>
       </c>
       <c r="C987" t="n">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>Customer service support 1</t>
+          <t>Customer service support 2</t>
         </is>
       </c>
       <c r="C988" t="n">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>Programming/software development 4</t>
+          <t>Programming/software development 2</t>
         </is>
       </c>
       <c r="C992" t="n">
@@ -15318,7 +15318,7 @@
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Programming/software development 2</t>
+          <t>Programming/software development 4</t>
         </is>
       </c>
       <c r="C993" t="n">
@@ -15363,7 +15363,7 @@
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>Programming/software development 2</t>
+          <t>Programming/software development 6</t>
         </is>
       </c>
       <c r="C996" t="n">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>Programming/software development 6</t>
+          <t>Programming/software development 3</t>
         </is>
       </c>
       <c r="C998" t="n">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>Programming/software development 3</t>
+          <t>Programming/software development 2</t>
         </is>
       </c>
       <c r="C999" t="n">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>Budgeting and forecasting 2</t>
+          <t>Budgeting and forecasting 6</t>
         </is>
       </c>
       <c r="C1000" t="n">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>Budgeting and forecasting 5</t>
+          <t>Budgeting and forecasting 2</t>
         </is>
       </c>
       <c r="C1002" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>Budgeting and forecasting 6</t>
+          <t>Budgeting and forecasting 4</t>
         </is>
       </c>
       <c r="C1003" t="n">
@@ -15483,7 +15483,7 @@
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>Budgeting and forecasting 4</t>
+          <t>Budgeting and forecasting 5</t>
         </is>
       </c>
       <c r="C1004" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Database design 2</t>
+          <t>Database design 3</t>
         </is>
       </c>
       <c r="C1005" t="n">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>Database design 3</t>
+          <t>Database design 2</t>
         </is>
       </c>
       <c r="C1006" t="n">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>Programming/software development 2</t>
+          <t>Programming/software development 6</t>
         </is>
       </c>
       <c r="C1008" t="n">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>Programming/software development 6</t>
+          <t>Programming/software development 3</t>
         </is>
       </c>
       <c r="C1010" t="n">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>Programming/software development 3</t>
+          <t>Programming/software development 2</t>
         </is>
       </c>
       <c r="C1011" t="n">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>Consultancy 5</t>
+          <t>Consultancy 6</t>
         </is>
       </c>
       <c r="C1013" t="n">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>Consultancy 4</t>
+          <t>Consultancy 5</t>
         </is>
       </c>
       <c r="C1014" t="n">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>Consultancy 6</t>
+          <t>Consultancy 4</t>
         </is>
       </c>
       <c r="C1015" t="n">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C1017" t="n">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C1018" t="n">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>Software design 2</t>
+          <t>Software design 3</t>
         </is>
       </c>
       <c r="C1019" t="n">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>Software design 5</t>
+          <t>Software design 2</t>
         </is>
       </c>
       <c r="C1020" t="n">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>Software design 4</t>
+          <t>Software design 5</t>
         </is>
       </c>
       <c r="C1021" t="n">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>Software design 3</t>
+          <t>Software design 4</t>
         </is>
       </c>
       <c r="C1022" t="n">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>User acceptance testing 2</t>
+          <t>User acceptance testing 3</t>
         </is>
       </c>
       <c r="C1023" t="n">
@@ -15783,7 +15783,7 @@
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>User acceptance testing 3</t>
+          <t>User acceptance testing 2</t>
         </is>
       </c>
       <c r="C1024" t="n">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>Functional testing 3</t>
+          <t>Functional testing 2</t>
         </is>
       </c>
       <c r="C1026" t="n">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>Functional testing 2</t>
+          <t>Functional testing 4</t>
         </is>
       </c>
       <c r="C1027" t="n">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>Functional testing 4</t>
+          <t>Functional testing 3</t>
         </is>
       </c>
       <c r="C1028" t="n">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>Functional testing 1</t>
+          <t>Functional testing 3</t>
         </is>
       </c>
       <c r="C1031" t="n">
@@ -15903,7 +15903,7 @@
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>Functional testing 3</t>
+          <t>Functional testing 1</t>
         </is>
       </c>
       <c r="C1032" t="n">
@@ -15933,7 +15933,7 @@
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>Functional testing 6</t>
+          <t>Functional testing 4</t>
         </is>
       </c>
       <c r="C1034" t="n">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>Functional testing 4</t>
+          <t>Functional testing 6</t>
         </is>
       </c>
       <c r="C1035" t="n">
@@ -15978,7 +15978,7 @@
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>Functional testing 1</t>
+          <t>Functional testing 3</t>
         </is>
       </c>
       <c r="C1037" t="n">
@@ -15993,7 +15993,7 @@
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>Functional testing 3</t>
+          <t>Functional testing 1</t>
         </is>
       </c>
       <c r="C1038" t="n">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>Data science 5</t>
+          <t>Data science 4</t>
         </is>
       </c>
       <c r="C1041" t="n">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>Data science 4</t>
+          <t>Data science 5</t>
         </is>
       </c>
       <c r="C1042" t="n">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>Data modelling and design 2</t>
+          <t>Data modelling and design 4</t>
         </is>
       </c>
       <c r="C1045" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>Data modelling and design 4</t>
+          <t>Data modelling and design 2</t>
         </is>
       </c>
       <c r="C1046" t="n">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>Portfolio, programme and project support 4</t>
+          <t>Portfolio, programme and project support 5</t>
         </is>
       </c>
       <c r="C1050" t="n">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>Portfolio, programme and project support 3</t>
+          <t>Portfolio, programme and project support 2</t>
         </is>
       </c>
       <c r="C1051" t="n">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>Portfolio, programme and project support 5</t>
+          <t>Portfolio, programme and project support 3</t>
         </is>
       </c>
       <c r="C1052" t="n">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>Portfolio, programme and project support 2</t>
+          <t>Portfolio, programme and project support 4</t>
         </is>
       </c>
       <c r="C1053" t="n">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>Portfolio, programme and project support 3</t>
+          <t>Portfolio, programme and project support 2</t>
         </is>
       </c>
       <c r="C1058" t="n">
@@ -16308,7 +16308,7 @@
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>Portfolio, programme and project support 2</t>
+          <t>Portfolio, programme and project support 3</t>
         </is>
       </c>
       <c r="C1059" t="n">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>Business process improvement 4</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C1063" t="n">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 4</t>
         </is>
       </c>
       <c r="C1064" t="n">
@@ -16398,7 +16398,7 @@
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C1065" t="n">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C1066" t="n">
@@ -16428,7 +16428,7 @@
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C1067" t="n">
@@ -16443,7 +16443,7 @@
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>Deployment 5</t>
+          <t>Deployment 2</t>
         </is>
       </c>
       <c r="C1068" t="n">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>Deployment 2</t>
+          <t>Deployment 5</t>
         </is>
       </c>
       <c r="C1069" t="n">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C1072" t="n">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C1073" t="n">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C1075" t="n">
@@ -16578,7 +16578,7 @@
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C1077" t="n">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 5</t>
         </is>
       </c>
       <c r="C1078" t="n">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>Penetration testing 5</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C1079" t="n">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C1081" t="n">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 5</t>
         </is>
       </c>
       <c r="C1083" t="n">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>Penetration testing 5</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C1084" t="n">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C1085" t="n">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>Solution architecture 4</t>
+          <t>Solution architecture 6</t>
         </is>
       </c>
       <c r="C1087" t="n">
@@ -16743,7 +16743,7 @@
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>Solution architecture 6</t>
+          <t>Solution architecture 4</t>
         </is>
       </c>
       <c r="C1088" t="n">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>Vulnerability assessment 2</t>
+          <t>Vulnerability assessment 5</t>
         </is>
       </c>
       <c r="C1092" t="n">
@@ -16818,7 +16818,7 @@
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>Vulnerability assessment 5</t>
+          <t>Vulnerability assessment 2</t>
         </is>
       </c>
       <c r="C1093" t="n">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C1098" t="n">
@@ -16908,7 +16908,7 @@
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C1099" t="n">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C1100" t="n">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C1101" t="n">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>Storage management 2</t>
+          <t>Storage management 3</t>
         </is>
       </c>
       <c r="C1104" t="n">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>Storage management 3</t>
+          <t>Storage management 2</t>
         </is>
       </c>
       <c r="C1105" t="n">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>Storage management 2</t>
+          <t>Storage management 3</t>
         </is>
       </c>
       <c r="C1106" t="n">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>Storage management 4</t>
+          <t>Storage management 2</t>
         </is>
       </c>
       <c r="C1108" t="n">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Storage management 3</t>
+          <t>Storage management 4</t>
         </is>
       </c>
       <c r="C1109" t="n">
@@ -17073,7 +17073,7 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>Storage management 2</t>
+          <t>Storage management 3</t>
         </is>
       </c>
       <c r="C1110" t="n">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>Storage management 4</t>
+          <t>Storage management 2</t>
         </is>
       </c>
       <c r="C1111" t="n">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>Storage management 3</t>
+          <t>Storage management 4</t>
         </is>
       </c>
       <c r="C1112" t="n">
@@ -17163,7 +17163,7 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>Infrastructure operations 3</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C1116" t="n">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 4</t>
         </is>
       </c>
       <c r="C1117" t="n">
@@ -17193,7 +17193,7 @@
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>Infrastructure operations 4</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C1118" t="n">
@@ -17208,7 +17208,7 @@
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 3</t>
         </is>
       </c>
       <c r="C1119" t="n">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C1120" t="n">
@@ -17238,7 +17238,7 @@
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C1121" t="n">
@@ -17253,7 +17253,7 @@
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>Deployment 5</t>
+          <t>Deployment 2</t>
         </is>
       </c>
       <c r="C1122" t="n">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>Deployment 2</t>
+          <t>Deployment 5</t>
         </is>
       </c>
       <c r="C1123" t="n">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>Deployment 3</t>
+          <t>Deployment 2</t>
         </is>
       </c>
       <c r="C1127" t="n">
@@ -17343,7 +17343,7 @@
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>Deployment 2</t>
+          <t>Deployment 6</t>
         </is>
       </c>
       <c r="C1128" t="n">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>Deployment 6</t>
+          <t>Deployment 3</t>
         </is>
       </c>
       <c r="C1130" t="n">
@@ -17418,7 +17418,7 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C1133" t="n">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C1134" t="n">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>Machine learning 3</t>
+          <t>Machine learning 2</t>
         </is>
       </c>
       <c r="C1135" t="n">
@@ -17463,7 +17463,7 @@
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>Machine learning 2</t>
+          <t>Machine learning 5</t>
         </is>
       </c>
       <c r="C1136" t="n">
@@ -17478,7 +17478,7 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>Machine learning 5</t>
+          <t>Machine learning 3</t>
         </is>
       </c>
       <c r="C1137" t="n">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>Machine learning 2</t>
+          <t>Machine learning 6</t>
         </is>
       </c>
       <c r="C1141" t="n">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>Machine learning 4</t>
+          <t>Machine learning 2</t>
         </is>
       </c>
       <c r="C1142" t="n">
@@ -17583,7 +17583,7 @@
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>Machine learning 6</t>
+          <t>Machine learning 4</t>
         </is>
       </c>
       <c r="C1144" t="n">
@@ -17598,7 +17598,7 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>Machine learning 3</t>
+          <t>Machine learning 2</t>
         </is>
       </c>
       <c r="C1145" t="n">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>Machine learning 2</t>
+          <t>Machine learning 3</t>
         </is>
       </c>
       <c r="C1146" t="n">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>Functional testing 1</t>
+          <t>Functional testing 3</t>
         </is>
       </c>
       <c r="C1149" t="n">
@@ -17673,7 +17673,7 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>Functional testing 3</t>
+          <t>Functional testing 1</t>
         </is>
       </c>
       <c r="C1150" t="n">
@@ -17748,7 +17748,7 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>Enterprise and business architecture 5</t>
+          <t>Enterprise and business architecture 6</t>
         </is>
       </c>
       <c r="C1155" t="n">
@@ -17763,7 +17763,7 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>Enterprise and business architecture 6</t>
+          <t>Enterprise and business architecture 5</t>
         </is>
       </c>
       <c r="C1156" t="n">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 5</t>
         </is>
       </c>
       <c r="C1159" t="n">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>Network design 5</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C1160" t="n">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C1162" t="n">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>Change control 2</t>
+          <t>Change control 3</t>
         </is>
       </c>
       <c r="C1163" t="n">
@@ -17883,7 +17883,7 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>Change control 5</t>
+          <t>Change control 6</t>
         </is>
       </c>
       <c r="C1164" t="n">
@@ -17898,7 +17898,7 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>Change control 6</t>
+          <t>Change control 4</t>
         </is>
       </c>
       <c r="C1165" t="n">
@@ -17913,7 +17913,7 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>Change control 4</t>
+          <t>Change control 2</t>
         </is>
       </c>
       <c r="C1166" t="n">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>Change control 3</t>
+          <t>Change control 5</t>
         </is>
       </c>
       <c r="C1167" t="n">
@@ -17958,7 +17958,7 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C1169" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C1170" t="n">
@@ -17988,7 +17988,7 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C1171" t="n">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C1172" t="n">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>Service level management 3</t>
+          <t>Service level management 2</t>
         </is>
       </c>
       <c r="C1176" t="n">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Service level management 4</t>
+          <t>Service level management 3</t>
         </is>
       </c>
       <c r="C1177" t="n">
@@ -18093,7 +18093,7 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>Service level management 2</t>
+          <t>Service level management 4</t>
         </is>
       </c>
       <c r="C1178" t="n">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>Infrastructure operations 3</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C1181" t="n">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 4</t>
         </is>
       </c>
       <c r="C1182" t="n">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>Infrastructure operations 4</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C1183" t="n">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 3</t>
         </is>
       </c>
       <c r="C1184" t="n">
@@ -18213,7 +18213,7 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>Professional development 5</t>
+          <t>Professional development 4</t>
         </is>
       </c>
       <c r="C1186" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>Professional development 4</t>
+          <t>Professional development 5</t>
         </is>
       </c>
       <c r="C1187" t="n">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Professional development 5</t>
+          <t>Professional development 4</t>
         </is>
       </c>
       <c r="C1188" t="n">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>Professional development 4</t>
+          <t>Professional development 5</t>
         </is>
       </c>
       <c r="C1189" t="n">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>Customer service support 2</t>
+          <t>Customer service support 1</t>
         </is>
       </c>
       <c r="C1190" t="n">
@@ -18288,7 +18288,7 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Customer service support 1</t>
+          <t>Customer service support 2</t>
         </is>
       </c>
       <c r="C1191" t="n">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>Service level management 4</t>
+          <t>Service level management 2</t>
         </is>
       </c>
       <c r="C1192" t="n">
@@ -18318,7 +18318,7 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>Service level management 7</t>
+          <t>Service level management 6</t>
         </is>
       </c>
       <c r="C1193" t="n">
@@ -18333,7 +18333,7 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>Service level management 3</t>
+          <t>Service level management 7</t>
         </is>
       </c>
       <c r="C1194" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Service level management 6</t>
+          <t>Service level management 3</t>
         </is>
       </c>
       <c r="C1196" t="n">
@@ -18378,7 +18378,7 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>Service level management 2</t>
+          <t>Service level management 4</t>
         </is>
       </c>
       <c r="C1197" t="n">
@@ -18393,7 +18393,7 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Enterprise and business architecture 5</t>
+          <t>Enterprise and business architecture 6</t>
         </is>
       </c>
       <c r="C1198" t="n">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Enterprise and business architecture 6</t>
+          <t>Enterprise and business architecture 5</t>
         </is>
       </c>
       <c r="C1199" t="n">
@@ -18423,7 +18423,7 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C1200" t="n">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C1202" t="n">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Data engineering 3</t>
+          <t>Data engineering 4</t>
         </is>
       </c>
       <c r="C1203" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Data engineering 4</t>
+          <t>Data engineering 2</t>
         </is>
       </c>
       <c r="C1204" t="n">
@@ -18498,7 +18498,7 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>Data engineering 2</t>
+          <t>Data engineering 3</t>
         </is>
       </c>
       <c r="C1205" t="n">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>Data analytics 5</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C1206" t="n">
@@ -18528,7 +18528,7 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C1207" t="n">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Data analytics 4</t>
+          <t>Data analytics 6</t>
         </is>
       </c>
       <c r="C1208" t="n">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>Data analytics 6</t>
+          <t>Data analytics 5</t>
         </is>
       </c>
       <c r="C1209" t="n">
@@ -18573,7 +18573,7 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 4</t>
         </is>
       </c>
       <c r="C1210" t="n">
@@ -18588,7 +18588,7 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Data engineering 3</t>
+          <t>Data engineering 2</t>
         </is>
       </c>
       <c r="C1211" t="n">
@@ -18603,7 +18603,7 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Data engineering 2</t>
+          <t>Data engineering 3</t>
         </is>
       </c>
       <c r="C1212" t="n">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Learning and development management 7</t>
+          <t>Learning and development management 2</t>
         </is>
       </c>
       <c r="C1213" t="n">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Learning and development management 2</t>
+          <t>Learning and development management 6</t>
         </is>
       </c>
       <c r="C1214" t="n">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Learning and development management 6</t>
+          <t>Learning and development management 7</t>
         </is>
       </c>
       <c r="C1217" t="n">
@@ -18708,7 +18708,7 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Technology service management 7</t>
+          <t>Technology service management 6</t>
         </is>
       </c>
       <c r="C1219" t="n">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Technology service management 5</t>
+          <t>Technology service management 7</t>
         </is>
       </c>
       <c r="C1220" t="n">
@@ -18738,7 +18738,7 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Technology service management 6</t>
+          <t>Technology service management 5</t>
         </is>
       </c>
       <c r="C1221" t="n">
@@ -18753,7 +18753,7 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Customer service support 2</t>
+          <t>Customer service support 1</t>
         </is>
       </c>
       <c r="C1222" t="n">
@@ -18768,7 +18768,7 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Customer service support 1</t>
+          <t>Customer service support 2</t>
         </is>
       </c>
       <c r="C1223" t="n">
@@ -18813,7 +18813,7 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Security operations 3</t>
+          <t>Security operations 2</t>
         </is>
       </c>
       <c r="C1226" t="n">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Security operations 5</t>
+          <t>Security operations 1</t>
         </is>
       </c>
       <c r="C1228" t="n">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Security operations 1</t>
+          <t>Security operations 3</t>
         </is>
       </c>
       <c r="C1229" t="n">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Security operations 2</t>
+          <t>Security operations 5</t>
         </is>
       </c>
       <c r="C1230" t="n">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Infrastructure operations 3</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C1231" t="n">
@@ -18903,7 +18903,7 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 4</t>
         </is>
       </c>
       <c r="C1232" t="n">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Infrastructure operations 4</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C1233" t="n">
@@ -18933,7 +18933,7 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 3</t>
         </is>
       </c>
       <c r="C1234" t="n">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Application support 3</t>
+          <t>Application support 5</t>
         </is>
       </c>
       <c r="C1238" t="n">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Application support 2</t>
+          <t>Application support 3</t>
         </is>
       </c>
       <c r="C1239" t="n">
@@ -19023,7 +19023,7 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Application support 5</t>
+          <t>Application support 4</t>
         </is>
       </c>
       <c r="C1240" t="n">
@@ -19038,7 +19038,7 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>Application support 4</t>
+          <t>Application support 2</t>
         </is>
       </c>
       <c r="C1241" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>User research 2</t>
+          <t>User research 3</t>
         </is>
       </c>
       <c r="C1243" t="n">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>User research 3</t>
+          <t>User research 2</t>
         </is>
       </c>
       <c r="C1244" t="n">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>User research 2</t>
+          <t>User research 3</t>
         </is>
       </c>
       <c r="C1245" t="n">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>User research 3</t>
+          <t>User research 2</t>
         </is>
       </c>
       <c r="C1246" t="n">
@@ -19143,7 +19143,7 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Animation development 2</t>
+          <t>Animation development 4</t>
         </is>
       </c>
       <c r="C1248" t="n">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Animation development 4</t>
+          <t>Animation development 2</t>
         </is>
       </c>
       <c r="C1249" t="n">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Systems integration and build 3</t>
+          <t>Systems integration and build 2</t>
         </is>
       </c>
       <c r="C1252" t="n">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Systems integration and build 2</t>
+          <t>Systems integration and build 4</t>
         </is>
       </c>
       <c r="C1253" t="n">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>Systems integration and build 4</t>
+          <t>Systems integration and build 3</t>
         </is>
       </c>
       <c r="C1254" t="n">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>User experience design 6</t>
+          <t>User experience design 5</t>
         </is>
       </c>
       <c r="C1257" t="n">
@@ -19323,7 +19323,7 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>User experience design 5</t>
+          <t>User experience design 6</t>
         </is>
       </c>
       <c r="C1260" t="n">
@@ -19353,7 +19353,7 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>Animation development 2</t>
+          <t>Animation development 4</t>
         </is>
       </c>
       <c r="C1262" t="n">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>Animation development 4</t>
+          <t>Animation development 2</t>
         </is>
       </c>
       <c r="C1263" t="n">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>User experience design 2</t>
+          <t>User experience design 4</t>
         </is>
       </c>
       <c r="C1267" t="n">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>User experience design 4</t>
+          <t>User experience design 2</t>
         </is>
       </c>
       <c r="C1268" t="n">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>User experience design 2</t>
+          <t>User experience design 4</t>
         </is>
       </c>
       <c r="C1272" t="n">
@@ -19518,7 +19518,7 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>User experience design 4</t>
+          <t>User experience design 2</t>
         </is>
       </c>
       <c r="C1273" t="n">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>Animation development 2</t>
+          <t>Animation development 4</t>
         </is>
       </c>
       <c r="C1281" t="n">
@@ -19653,7 +19653,7 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>Animation development 4</t>
+          <t>Animation development 2</t>
         </is>
       </c>
       <c r="C1282" t="n">
@@ -19683,7 +19683,7 @@
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>Marketing management 6</t>
+          <t>Marketing management 5</t>
         </is>
       </c>
       <c r="C1284" t="n">
@@ -19713,7 +19713,7 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Marketing management 5</t>
+          <t>Marketing management 6</t>
         </is>
       </c>
       <c r="C1286" t="n">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>User experience design 2</t>
+          <t>User experience design 4</t>
         </is>
       </c>
       <c r="C1288" t="n">
@@ -19758,7 +19758,7 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>User experience design 4</t>
+          <t>User experience design 2</t>
         </is>
       </c>
       <c r="C1289" t="n">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Data engineering 3</t>
+          <t>Data engineering 4</t>
         </is>
       </c>
       <c r="C1291" t="n">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>Data engineering 4</t>
+          <t>Data engineering 2</t>
         </is>
       </c>
       <c r="C1292" t="n">
@@ -19818,7 +19818,7 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>Data engineering 2</t>
+          <t>Data engineering 3</t>
         </is>
       </c>
       <c r="C1293" t="n">
